--- a/cde-facilities-toolset/references/Standards_for_Facilities_v2.xlsx
+++ b/cde-facilities-toolset/references/Standards_for_Facilities_v2.xlsx
@@ -108,7 +108,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -137,6 +137,11 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -338,7 +343,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -467,30 +472,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -500,6 +499,3065 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors/>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>952500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>809625</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>952500</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2600325" y="1714500"/>
+          <a:ext cx="790575" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1152525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>819150</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1152525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Straight Connector 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2609850" y="1914525"/>
+          <a:ext cx="790575" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1381125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>828675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1381125</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Straight Connector 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2619375" y="2143125"/>
+          <a:ext cx="790575" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>147192</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>123827</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>695323</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>666751</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9" descr="http://upload.wikimedia.org/wikipedia/commons/thumb/7/77/International_Symbol_of_Access.svg/2000px-International_Symbol_of_Access.svg.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2728467" y="4743452"/>
+          <a:ext cx="548131" cy="542924"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>32214</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1552575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>794214</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1552575</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="Straight Connector 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2311793" y="9012041"/>
+          <a:ext cx="762000" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1190625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>833437</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1190625</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="Straight Connector 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2509838" y="13156406"/>
+          <a:ext cx="776287" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>128427</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>1043898</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>676558</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>1586822</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8" descr="http://upload.wikimedia.org/wikipedia/commons/thumb/7/77/International_Symbol_of_Access.svg/2000px-International_Symbol_of_Access.svg.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2408006" y="76055949"/>
+          <a:ext cx="548131" cy="542924"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>10703</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>32107</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1702437</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>4075902</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8272838" y="72614747"/>
+          <a:ext cx="1691734" cy="4045449"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>663541</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>153138</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>931096</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>4491343</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5500957" y="72735778"/>
+          <a:ext cx="1979914" cy="4341805"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>768801</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>96320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1040242</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>5019354</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5606217" y="77880253"/>
+          <a:ext cx="1983800" cy="4923034"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>21406</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>107022</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1674844</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>4748294</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Picture 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8283541" y="77890955"/>
+          <a:ext cx="1653438" cy="4644775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>64212</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>149832</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1155842</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>2903423</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Picture 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4901628" y="99680731"/>
+          <a:ext cx="2803989" cy="3615061"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>53512</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>310364</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1645835</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>1418728</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8315647" y="99841263"/>
+          <a:ext cx="1592323" cy="1969725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>470898</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>85618</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>891872</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>4409326</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5308314" y="109740843"/>
+          <a:ext cx="2133333" cy="4323708"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>53512</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>10702</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1595438</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>2349413</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8923668" y="133241640"/>
+          <a:ext cx="1541926" cy="2338711"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>103545</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>2311685</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1654969</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>4476458</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8973701" y="135542623"/>
+          <a:ext cx="1551424" cy="2169053"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>32107</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>96319</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1683566</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>1525069</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8294242" y="136036263"/>
+          <a:ext cx="1651459" cy="1433767"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>42809</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>181938</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1702854</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>1567392</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8304944" y="138551292"/>
+          <a:ext cx="1660045" cy="1397932"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>288961</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>53510</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1604155</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>1330211</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8551096" y="144769297"/>
+          <a:ext cx="1315194" cy="1276701"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>288960</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>53510</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1318383" cy="1279797"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Picture 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9159116" y="190874979"/>
+          <a:ext cx="1318383" cy="1279797"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>85619</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>10702</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1575163</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>1846430</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Picture 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8347754" y="192929410"/>
+          <a:ext cx="1489544" cy="1851488"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>47877</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>64213</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1680252</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>1541123</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Picture 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8310012" y="173023230"/>
+          <a:ext cx="1632375" cy="1476910"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>139129</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>107022</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1605796</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>1518454</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Picture 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8401264" y="167447359"/>
+          <a:ext cx="1466667" cy="1419048"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>85619</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>53512</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1606881</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>2651360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Picture 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6635394" y="128116602"/>
+          <a:ext cx="1521262" cy="2597848"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>117724</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>2020702</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1605337</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>4055589</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Picture 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4955140" y="130083792"/>
+          <a:ext cx="1487613" cy="2044618"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>64214</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>171235</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1643744</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>1989644</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Picture 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4901630" y="128234325"/>
+          <a:ext cx="1579530" cy="1824629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>791967</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>139129</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>808662</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>2364516</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="Picture 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5629383" y="139332556"/>
+          <a:ext cx="1729054" cy="2228162"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>331769</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>128427</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1095600</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>2299856</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Picture 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5169185" y="136892444"/>
+          <a:ext cx="2476190" cy="2171429"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>224748</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>42809</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1284271</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>2758835</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="Picture 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5062164" y="148129803"/>
+          <a:ext cx="2771882" cy="2716026"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>432835</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>2793288</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>898989</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>5053311</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="Picture 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5270251" y="150880282"/>
+          <a:ext cx="2178513" cy="2270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>181939</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>50858</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1316378</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>2780019</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="Picture 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5019355" y="173009875"/>
+          <a:ext cx="2846798" cy="2729161"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>160534</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>149832</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1627201</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>1561264</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Picture 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6710309" y="171054017"/>
+          <a:ext cx="1466667" cy="1419048"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>107023</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>74915</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1573690</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>1486347</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Picture 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4944439" y="170979100"/>
+          <a:ext cx="1466667" cy="1419048"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>42812</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>243622</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1651056</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>2702804</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Picture 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4891903" y="219110804"/>
+          <a:ext cx="1608244" cy="2459182"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>21405</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>117726</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1647333</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>2299816</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Picture 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6571180" y="183329496"/>
+          <a:ext cx="1625928" cy="2183258"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>481601</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>117725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1154119</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>2819529</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Picture 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5319017" y="187107388"/>
+          <a:ext cx="2384877" cy="2701804"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>406684</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>95884</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1080926</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>2329930</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Picture 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5244100" y="190424648"/>
+          <a:ext cx="2386601" cy="2240696"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>149831</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>181937</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1380589</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>2530540</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Picture 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4987247" y="196546768"/>
+          <a:ext cx="1230758" cy="2348603"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>331769</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>2504326</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1436531</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>4521895</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Picture 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5169185" y="198869157"/>
+          <a:ext cx="1104762" cy="2019048"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>64214</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>203342</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1661681</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>2707668</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="Picture 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6613989" y="196568173"/>
+          <a:ext cx="1597467" cy="2504326"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>331771</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>2664858</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1392583</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>4786481</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Picture 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6881546" y="199029689"/>
+          <a:ext cx="1060812" cy="2121623"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>64213</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>171236</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1637443</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>1594634</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8342304" y="250514213"/>
+          <a:ext cx="1573230" cy="1423398"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>82055</xdr:colOff>
+      <xdr:row>164</xdr:row>
+      <xdr:rowOff>352107</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1637089</xdr:colOff>
+      <xdr:row>164</xdr:row>
+      <xdr:rowOff>2022724</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Picture 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4919471" y="271065450"/>
+          <a:ext cx="3267393" cy="1670617"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>96323</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>726643</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1621982</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>2664861</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="Picture 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4933739" y="274019227"/>
+          <a:ext cx="3238018" cy="1938218"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>192641</xdr:colOff>
+      <xdr:row>164</xdr:row>
+      <xdr:rowOff>19100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1583932</xdr:colOff>
+      <xdr:row>164</xdr:row>
+      <xdr:rowOff>2365198</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8454776" y="270732443"/>
+          <a:ext cx="1391291" cy="2346098"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1091629</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>21404</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>263</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>1123735</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9353764" y="273313988"/>
+          <a:ext cx="624889" cy="1102331"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>64212</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>113408</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1059522</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>1155166</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 67">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8326347" y="273405992"/>
+          <a:ext cx="995310" cy="1041758"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>560369</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>1262866</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1669550</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>2343793</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 68">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8822504" y="274555450"/>
+          <a:ext cx="1109181" cy="1080927"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>64213</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>2256881</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1038118</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>3341457</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 69">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8326348" y="275549465"/>
+          <a:ext cx="973905" cy="1084576"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>470898</xdr:colOff>
+      <xdr:row>169</xdr:row>
+      <xdr:rowOff>214048</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>931096</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>1072854</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 70">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5308314" y="279403570"/>
+          <a:ext cx="2172557" cy="2185885"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>824069</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>1127513</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>695645</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>1658178</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5661485" y="281644114"/>
+          <a:ext cx="1583935" cy="1942291"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>13055</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>45535</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1123735</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>1134437</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="42" name="Picture 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8275190" y="281878513"/>
+          <a:ext cx="1110680" cy="1088902"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>417438</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>1057408</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1509018</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>2012022</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="43" name="Picture 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8679573" y="282890386"/>
+          <a:ext cx="1091580" cy="954614"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>205341</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>1155700</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1391291" cy="1803400"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9075497" y="284333950"/>
+          <a:ext cx="1391291" cy="1803400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>109705</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="762000"/>
+          <a:ext cx="6391275" cy="6586705"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="981075" y="7810500"/>
+          <a:ext cx="8029575" cy="2476500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="11239500"/>
+          <a:ext cx="3743325" cy="2505075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>369559</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>201202</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="3417559" cy="1915702"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>723900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="752475" y="3228975"/>
+          <a:ext cx="847725" cy="1495425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>523875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2724150" y="3028950"/>
+          <a:ext cx="847725" cy="1495425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>523875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7962900" y="3028950"/>
+          <a:ext cx="1428750" cy="1495425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>466725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7620000" y="657225"/>
+          <a:ext cx="923925" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6019800" y="3990975"/>
+          <a:ext cx="838200" cy="933450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -764,7 +3822,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -774,56 +3832,53 @@
   <cols>
     <col width="34.28515625" customWidth="1" min="1" max="1"/>
     <col width="12.7109375" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="4"/>
-    <col width="25.85546875" customWidth="1" min="5" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="25.7109375" customWidth="1" min="4" max="4"/>
+    <col width="25.85546875" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1">
-      <c r="A1" s="33" t="n"/>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="46" t="n"/>
       <c r="B1" s="18" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
-      <c r="C1" s="46" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>Program Access
-(built/altered on or before 6/3/1977)
-No measurable standard.
-Observational review only (Section 504)</t>
-        </is>
-      </c>
-      <c r="D1" s="19" t="inlineStr">
-        <is>
-          <t>ANSI (6/77)
-6/4/1977 - 1/17/1991</t>
-        </is>
-      </c>
-      <c r="E1" s="19" t="inlineStr">
+(on or before 6/3/1977)</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>ANSI
+(6/4/1977 - 1/17/1991)</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>UFAS
-1/18/1991 - 1/26/1992</t>
-        </is>
-      </c>
-      <c r="F1" s="19" t="inlineStr">
+(1/18/1991 - 1/26/1992)</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>1991 ADA
-1/27/1992 - 9/14/2010</t>
-        </is>
-      </c>
-      <c r="G1" s="46" t="inlineStr">
+(1/27/1992 - 9/14/2010)</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>ADAAG
-(applies with 1991 ADA:
-1/27/1992 - 9/14/2010)</t>
-        </is>
-      </c>
-      <c r="H1" s="19" t="inlineStr">
+(1/27/1992 - 9/14/2010)</t>
+        </is>
+      </c>
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>2010 ADA
-On/after 3/15/2012
-(9/15/2010 - 3/14/2012: UFAS, 1991 ADA, or 2010 ADA permitted)</t>
+(on or after 3/15/2012)</t>
         </is>
       </c>
     </row>
@@ -836,8 +3891,7 @@
       <c r="B2" s="40" t="n"/>
       <c r="C2" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D2" s="35" t="inlineStr">
@@ -857,8 +3911,7 @@
       </c>
       <c r="G2" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H2" s="35" t="inlineStr">
@@ -1006,8 +4059,7 @@
       <c r="B6" s="34" t="n"/>
       <c r="C6" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D6" s="34" t="inlineStr">
@@ -1030,8 +4082,7 @@
       </c>
       <c r="G6" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H6" s="34" t="inlineStr">
@@ -1050,8 +4101,7 @@
       <c r="B7" s="25" t="n"/>
       <c r="C7" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D7" s="34" t="inlineStr">
@@ -1074,8 +4124,7 @@
       </c>
       <c r="G7" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H7" s="34" t="inlineStr">
@@ -1094,8 +4143,7 @@
       <c r="B8" s="34" t="n"/>
       <c r="C8" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D8" s="34" t="inlineStr">
@@ -1118,8 +4166,7 @@
       </c>
       <c r="G8" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H8" s="34" t="inlineStr">
@@ -1138,8 +4185,7 @@
       <c r="B9" s="40" t="n"/>
       <c r="C9" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D9" s="35" t="inlineStr">
@@ -1159,8 +4205,7 @@
       </c>
       <c r="G9" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H9" s="35" t="inlineStr">
@@ -1185,8 +4230,7 @@
       </c>
       <c r="C10" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D10" s="34" t="inlineStr">
@@ -1212,8 +4256,7 @@
       </c>
       <c r="G10" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H10" s="34" t="inlineStr">
@@ -1234,8 +4277,7 @@
       <c r="B11" s="17" t="n"/>
       <c r="C11" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D11" s="35" t="inlineStr">
@@ -1255,8 +4297,7 @@
       </c>
       <c r="G11" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H11" s="35" t="inlineStr">
@@ -1279,8 +4320,7 @@
       </c>
       <c r="C12" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D12" s="34" t="inlineStr">
@@ -1307,8 +4347,7 @@
       </c>
       <c r="G12" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H12" s="34" t="inlineStr">
@@ -1328,8 +4367,7 @@
       <c r="B13" s="25" t="n"/>
       <c r="C13" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D13" s="34" t="inlineStr">
@@ -1355,8 +4393,7 @@
       </c>
       <c r="G13" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H13" s="34" t="inlineStr">
@@ -1377,8 +4414,7 @@
       <c r="B14" s="17" t="n"/>
       <c r="C14" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D14" s="35" t="inlineStr">
@@ -1398,8 +4434,7 @@
       </c>
       <c r="G14" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H14" s="35" t="inlineStr">
@@ -1422,8 +4457,7 @@
       </c>
       <c r="C15" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D15" s="34" t="inlineStr">
@@ -1445,8 +4479,7 @@
       </c>
       <c r="G15" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H15" s="34" t="inlineStr">
@@ -1470,8 +4503,7 @@
       </c>
       <c r="C16" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D16" s="34" t="inlineStr">
@@ -1491,8 +4523,7 @@
       </c>
       <c r="G16" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H16" s="34" t="inlineStr">
@@ -1553,8 +4584,7 @@
       <c r="B18" s="17" t="n"/>
       <c r="C18" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D18" s="35" t="inlineStr">
@@ -1574,8 +4604,7 @@
       </c>
       <c r="G18" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H18" s="35" t="inlineStr">
@@ -1599,8 +4628,7 @@
       </c>
       <c r="C19" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D19" s="34" t="inlineStr">
@@ -1631,8 +4659,7 @@
       </c>
       <c r="G19" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H19" s="34" t="inlineStr">
@@ -1695,8 +4722,7 @@
       </c>
       <c r="C21" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D21" s="34" t="inlineStr">
@@ -1719,8 +4745,7 @@
       </c>
       <c r="G21" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H21" s="34" t="inlineStr">
@@ -1775,8 +4800,7 @@
       <c r="B23" s="17" t="n"/>
       <c r="C23" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D23" s="35" t="inlineStr">
@@ -1796,8 +4820,7 @@
       </c>
       <c r="G23" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H23" s="35" t="inlineStr">
@@ -1856,8 +4879,7 @@
       </c>
       <c r="C25" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D25" s="34" t="inlineStr">
@@ -1885,8 +4907,7 @@
       </c>
       <c r="G25" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H25" s="34" t="inlineStr">
@@ -1943,8 +4964,7 @@
       <c r="B27" s="17" t="n"/>
       <c r="C27" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D27" s="35" t="inlineStr">
@@ -1964,8 +4984,7 @@
       </c>
       <c r="G27" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H27" s="35" t="inlineStr">
@@ -2089,8 +5108,7 @@
       <c r="B31" s="17" t="n"/>
       <c r="C31" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D31" s="35" t="inlineStr">
@@ -2110,8 +5128,7 @@
       </c>
       <c r="G31" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H31" s="35" t="inlineStr">
@@ -2171,8 +5188,7 @@
       <c r="B33" s="17" t="n"/>
       <c r="C33" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D33" s="35" t="inlineStr">
@@ -2192,8 +5208,7 @@
       </c>
       <c r="G33" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H33" s="35" t="inlineStr">
@@ -2246,8 +5261,7 @@
       <c r="B35" s="17" t="n"/>
       <c r="C35" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D35" s="35" t="inlineStr">
@@ -2267,8 +5281,7 @@
       </c>
       <c r="G35" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H35" s="40" t="inlineStr">
@@ -2284,9 +5297,11 @@
         </is>
       </c>
       <c r="B36" s="49" t="n"/>
+      <c r="C36" s="49" t="n"/>
       <c r="D36" s="49" t="n"/>
       <c r="E36" s="49" t="n"/>
       <c r="F36" s="49" t="n"/>
+      <c r="G36" s="49" t="n"/>
       <c r="H36" s="50" t="n"/>
     </row>
     <row r="37" ht="228.75" customHeight="1">
@@ -2304,8 +5319,7 @@
       </c>
       <c r="C37" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D37" s="34" t="inlineStr">
@@ -2336,8 +5350,7 @@
       </c>
       <c r="G37" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H37" s="34" t="inlineStr">
@@ -2362,8 +5375,7 @@
       <c r="B38" s="25" t="n"/>
       <c r="C38" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D38" s="34" t="inlineStr">
@@ -2386,8 +5398,7 @@
       </c>
       <c r="G38" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H38" s="34" t="inlineStr">
@@ -2406,8 +5417,7 @@
       <c r="B39" s="25" t="n"/>
       <c r="C39" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D39" s="34" t="inlineStr">
@@ -2430,8 +5440,7 @@
       </c>
       <c r="G39" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H39" s="34" t="inlineStr">
@@ -2450,8 +5459,7 @@
       <c r="B40" s="17" t="n"/>
       <c r="C40" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D40" s="35" t="inlineStr">
@@ -2471,8 +5479,7 @@
       </c>
       <c r="G40" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H40" s="40" t="inlineStr">
@@ -2495,8 +5502,7 @@
       </c>
       <c r="C41" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D41" s="34" t="inlineStr">
@@ -2520,8 +5526,7 @@
       </c>
       <c r="G41" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H41" s="34" t="inlineStr">
@@ -2573,8 +5578,7 @@
       <c r="B43" s="17" t="n"/>
       <c r="C43" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D43" s="35" t="inlineStr">
@@ -2594,8 +5598,7 @@
       </c>
       <c r="G43" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H43" s="40" t="inlineStr">
@@ -2647,8 +5650,7 @@
       <c r="B45" s="17" t="n"/>
       <c r="C45" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D45" s="35" t="inlineStr">
@@ -2668,8 +5670,7 @@
       </c>
       <c r="G45" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H45" s="40" t="inlineStr">
@@ -2687,8 +5688,7 @@
       <c r="B46" s="25" t="n"/>
       <c r="C46" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D46" s="34" t="inlineStr">
@@ -2718,8 +5718,7 @@
       </c>
       <c r="G46" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H46" s="34" t="inlineStr">
@@ -2774,8 +5773,7 @@
       <c r="B48" s="17" t="n"/>
       <c r="C48" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D48" s="35" t="inlineStr">
@@ -2795,8 +5793,7 @@
       </c>
       <c r="G48" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H48" s="40" t="inlineStr">
@@ -2819,8 +5816,7 @@
       </c>
       <c r="C49" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
@@ -2843,8 +5839,7 @@
       </c>
       <c r="G49" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H49" s="34" t="inlineStr">
@@ -2870,8 +5865,7 @@
       </c>
       <c r="C50" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
@@ -2892,8 +5886,7 @@
       </c>
       <c r="G50" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H50" s="34" t="inlineStr">
@@ -2942,8 +5935,7 @@
       <c r="B52" s="17" t="n"/>
       <c r="C52" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D52" s="35" t="inlineStr">
@@ -2963,8 +5955,7 @@
       </c>
       <c r="G52" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H52" s="40" t="inlineStr">
@@ -3015,8 +6006,7 @@
       <c r="B54" s="17" t="n"/>
       <c r="C54" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D54" s="40" t="inlineStr">
@@ -3036,8 +6026,7 @@
       </c>
       <c r="G54" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H54" s="40" t="inlineStr">
@@ -3055,8 +6044,7 @@
       <c r="B55" s="25" t="n"/>
       <c r="C55" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D55" s="34" t="inlineStr">
@@ -3081,8 +6069,7 @@
       </c>
       <c r="G55" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H55" s="34" t="inlineStr">
@@ -3103,8 +6090,7 @@
       <c r="B56" s="17" t="n"/>
       <c r="C56" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D56" s="40" t="inlineStr">
@@ -3124,8 +6110,7 @@
       </c>
       <c r="G56" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H56" s="40" t="inlineStr">
@@ -3143,8 +6128,7 @@
       <c r="B57" s="25" t="n"/>
       <c r="C57" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D57" s="34" t="inlineStr">
@@ -3165,8 +6149,7 @@
       </c>
       <c r="G57" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H57" s="37" t="inlineStr">
@@ -3184,8 +6167,7 @@
       <c r="B58" s="17" t="n"/>
       <c r="C58" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D58" s="40" t="inlineStr">
@@ -3205,8 +6187,7 @@
       </c>
       <c r="G58" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H58" s="40" t="inlineStr">
@@ -3248,8 +6229,7 @@
       <c r="B60" s="17" t="n"/>
       <c r="C60" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D60" s="40" t="inlineStr">
@@ -3269,8 +6249,7 @@
       </c>
       <c r="G60" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H60" s="40" t="inlineStr">
@@ -3317,8 +6296,7 @@
       <c r="B62" s="25" t="n"/>
       <c r="C62" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D62" s="34" t="inlineStr">
@@ -3345,8 +6323,7 @@
       </c>
       <c r="G62" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H62" s="34" t="inlineStr">
@@ -3400,8 +6377,7 @@
       <c r="B64" s="17" t="n"/>
       <c r="C64" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D64" s="40" t="inlineStr">
@@ -3421,8 +6397,7 @@
       </c>
       <c r="G64" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H64" s="40" t="inlineStr">
@@ -3440,8 +6415,7 @@
       <c r="B65" s="25" t="n"/>
       <c r="C65" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D65" s="34" t="inlineStr">
@@ -3464,8 +6438,7 @@
       </c>
       <c r="G65" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H65" s="34" t="inlineStr">
@@ -3520,8 +6493,7 @@
       <c r="B67" s="17" t="n"/>
       <c r="C67" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D67" s="40" t="inlineStr">
@@ -3541,8 +6513,7 @@
       </c>
       <c r="G67" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H67" s="40" t="inlineStr">
@@ -3560,8 +6531,7 @@
       <c r="B68" s="25" t="n"/>
       <c r="C68" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D68" s="34" t="inlineStr">
@@ -3586,8 +6556,7 @@
       </c>
       <c r="G68" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H68" s="34" t="inlineStr">
@@ -3609,8 +6578,7 @@
       <c r="B69" s="17" t="n"/>
       <c r="C69" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D69" s="40" t="inlineStr">
@@ -3630,8 +6598,7 @@
       </c>
       <c r="G69" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H69" s="40" t="inlineStr">
@@ -3649,8 +6616,7 @@
       <c r="B70" s="25" t="n"/>
       <c r="C70" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D70" s="34" t="inlineStr">
@@ -3681,8 +6647,7 @@
       </c>
       <c r="G70" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H70" s="34" t="inlineStr">
@@ -3703,8 +6668,7 @@
       <c r="B71" s="17" t="n"/>
       <c r="C71" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D71" s="40" t="inlineStr">
@@ -3724,8 +6688,7 @@
       </c>
       <c r="G71" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H71" s="40" t="inlineStr">
@@ -3780,8 +6743,7 @@
       <c r="B74" s="25" t="n"/>
       <c r="C74" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D74" s="34" t="inlineStr">
@@ -3806,8 +6768,7 @@
       </c>
       <c r="G74" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H74" s="34" t="inlineStr">
@@ -3827,8 +6788,7 @@
       <c r="B75" s="17" t="n"/>
       <c r="C75" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D75" s="40" t="inlineStr">
@@ -3848,8 +6808,7 @@
       </c>
       <c r="G75" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H75" s="40" t="inlineStr">
@@ -3902,8 +6861,7 @@
       <c r="B77" s="25" t="n"/>
       <c r="C77" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D77" s="34" t="inlineStr">
@@ -3928,8 +6886,7 @@
       </c>
       <c r="G77" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H77" s="34" t="inlineStr">
@@ -3949,8 +6906,7 @@
       <c r="B78" s="17" t="n"/>
       <c r="C78" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D78" s="40" t="inlineStr">
@@ -3970,8 +6926,7 @@
       </c>
       <c r="G78" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H78" s="40" t="inlineStr">
@@ -3989,8 +6944,7 @@
       <c r="B79" s="25" t="n"/>
       <c r="C79" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D79" s="34" t="inlineStr">
@@ -4011,8 +6965,7 @@
       </c>
       <c r="G79" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H79" s="37" t="inlineStr">
@@ -4031,8 +6984,7 @@
       <c r="B80" s="17" t="n"/>
       <c r="C80" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D80" s="40" t="inlineStr">
@@ -4052,8 +7004,7 @@
       </c>
       <c r="G80" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H80" s="40" t="inlineStr">
@@ -4071,8 +7022,7 @@
       <c r="B81" s="25" t="n"/>
       <c r="C81" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D81" s="34" t="inlineStr">
@@ -4101,8 +7051,7 @@
       </c>
       <c r="G81" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H81" s="34" t="inlineStr">
@@ -4124,8 +7073,7 @@
       <c r="B82" s="17" t="n"/>
       <c r="C82" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D82" s="40" t="inlineStr">
@@ -4145,8 +7093,7 @@
       </c>
       <c r="G82" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H82" s="40" t="inlineStr">
@@ -4170,8 +7117,7 @@
       </c>
       <c r="C83" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D83" s="34" t="inlineStr">
@@ -4194,8 +7140,7 @@
       </c>
       <c r="G83" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H83" s="34" t="inlineStr">
@@ -4214,8 +7159,7 @@
       <c r="B84" s="17" t="n"/>
       <c r="C84" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D84" s="40" t="inlineStr">
@@ -4235,8 +7179,7 @@
       </c>
       <c r="G84" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H84" s="40" t="inlineStr">
@@ -4254,8 +7197,7 @@
       <c r="B85" s="25" t="n"/>
       <c r="C85" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D85" s="34" t="inlineStr">
@@ -4283,8 +7225,7 @@
       </c>
       <c r="G85" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H85" s="34" t="inlineStr">
@@ -4304,8 +7245,7 @@
       <c r="B86" s="17" t="n"/>
       <c r="C86" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D86" s="40" t="inlineStr">
@@ -4325,8 +7265,7 @@
       </c>
       <c r="G86" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H86" s="40" t="inlineStr">
@@ -4344,8 +7283,7 @@
       <c r="B87" s="25" t="n"/>
       <c r="C87" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D87" s="34" t="inlineStr">
@@ -4368,8 +7306,7 @@
       </c>
       <c r="G87" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H87" s="34" t="inlineStr">
@@ -4388,8 +7325,7 @@
       <c r="B88" s="25" t="n"/>
       <c r="C88" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D88" s="34" t="inlineStr">
@@ -4414,8 +7350,7 @@
       </c>
       <c r="G88" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H88" s="34" t="inlineStr">
@@ -4435,8 +7370,7 @@
       <c r="B89" s="25" t="n"/>
       <c r="C89" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D89" s="34" t="inlineStr">
@@ -4459,8 +7393,7 @@
       </c>
       <c r="G89" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H89" s="34" t="inlineStr">
@@ -4506,9 +7439,11 @@
         </is>
       </c>
       <c r="B91" s="49" t="n"/>
+      <c r="C91" s="49" t="n"/>
       <c r="D91" s="49" t="n"/>
       <c r="E91" s="49" t="n"/>
       <c r="F91" s="49" t="n"/>
+      <c r="G91" s="49" t="n"/>
       <c r="H91" s="50" t="n"/>
     </row>
     <row r="92" ht="30" customHeight="1">
@@ -4518,10 +7453,9 @@
         </is>
       </c>
       <c r="B92" s="39" t="n"/>
-      <c r="C92" s="52" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
+      <c r="C92" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D92" s="38" t="inlineStr">
@@ -4539,10 +7473,9 @@
           <t>Cite 4.16</t>
         </is>
       </c>
-      <c r="G92" s="52" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+      <c r="G92" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H92" s="38" t="inlineStr">
@@ -4594,8 +7527,7 @@
       <c r="B94" s="25" t="n"/>
       <c r="C94" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D94" s="34" t="inlineStr">
@@ -4615,8 +7547,7 @@
       </c>
       <c r="G94" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H94" s="34" t="inlineStr">
@@ -4633,10 +7564,9 @@
         </is>
       </c>
       <c r="B95" s="39" t="n"/>
-      <c r="C95" s="52" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
+      <c r="C95" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D95" s="38" t="inlineStr">
@@ -4654,10 +7584,9 @@
           <t>Cite 4.16</t>
         </is>
       </c>
-      <c r="G95" s="52" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+      <c r="G95" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H95" s="38" t="inlineStr">
@@ -4704,8 +7633,7 @@
       <c r="B97" s="25" t="n"/>
       <c r="C97" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D97" s="34" t="inlineStr">
@@ -4728,8 +7656,7 @@
       </c>
       <c r="G97" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H97" s="34" t="inlineStr">
@@ -4748,8 +7675,7 @@
       <c r="B98" s="25" t="n"/>
       <c r="C98" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D98" s="34" t="inlineStr">
@@ -4772,8 +7698,7 @@
       </c>
       <c r="G98" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H98" s="34" t="inlineStr">
@@ -4792,8 +7717,7 @@
       <c r="B99" s="25" t="n"/>
       <c r="C99" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D99" s="34" t="inlineStr">
@@ -4815,8 +7739,7 @@
       </c>
       <c r="G99" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H99" s="37" t="inlineStr">
@@ -4833,10 +7756,9 @@
         </is>
       </c>
       <c r="B100" s="39" t="n"/>
-      <c r="C100" s="52" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
+      <c r="C100" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D100" s="38" t="inlineStr">
@@ -4854,10 +7776,9 @@
           <t>Cite 4.16</t>
         </is>
       </c>
-      <c r="G100" s="52" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+      <c r="G100" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H100" s="38" t="inlineStr">
@@ -4940,8 +7861,7 @@
       <c r="B103" s="25" t="n"/>
       <c r="C103" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D103" s="34" t="inlineStr">
@@ -4966,8 +7886,7 @@
       </c>
       <c r="G103" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H103" s="34" t="inlineStr">
@@ -4986,10 +7905,9 @@
         </is>
       </c>
       <c r="B104" s="39" t="n"/>
-      <c r="C104" s="52" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
+      <c r="C104" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D104" s="38" t="inlineStr">
@@ -5007,10 +7925,9 @@
           <t>Cite 4.16</t>
         </is>
       </c>
-      <c r="G104" s="52" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+      <c r="G104" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H104" s="38" t="inlineStr">
@@ -5028,8 +7945,7 @@
       <c r="B105" s="25" t="n"/>
       <c r="C105" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D105" s="34" t="inlineStr">
@@ -5054,8 +7970,7 @@
       </c>
       <c r="G105" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H105" s="34" t="inlineStr">
@@ -5103,10 +8018,9 @@
         </is>
       </c>
       <c r="B107" s="39" t="n"/>
-      <c r="C107" s="52" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
+      <c r="C107" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D107" s="38" t="inlineStr">
@@ -5124,10 +8038,9 @@
           <t>Cite 4.16</t>
         </is>
       </c>
-      <c r="G107" s="52" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+      <c r="G107" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H107" s="38" t="inlineStr">
@@ -5145,8 +8058,7 @@
       <c r="B108" s="25" t="n"/>
       <c r="C108" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D108" s="34" t="inlineStr">
@@ -5167,8 +8079,7 @@
       </c>
       <c r="G108" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H108" s="37" t="inlineStr">
@@ -5190,10 +8101,9 @@
         </is>
       </c>
       <c r="B109" s="39" t="n"/>
-      <c r="C109" s="52" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
+      <c r="C109" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D109" s="38" t="inlineStr">
@@ -5211,10 +8121,9 @@
           <t>Cite 4.16</t>
         </is>
       </c>
-      <c r="G109" s="52" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+      <c r="G109" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H109" s="38" t="inlineStr">
@@ -5266,6 +8175,7 @@
           <t xml:space="preserve">SIX OR MORE STALLS (OR URINALS AND STALLS COMBINED) THERE MUST BE AT LEAST ONE AMBULATORY ACCESSIBLE STALL (213.3.1) </t>
         </is>
       </c>
+      <c r="C111" s="49" t="n"/>
       <c r="D111" s="49" t="n"/>
       <c r="E111" s="49" t="n"/>
       <c r="F111" s="50" t="n"/>
@@ -5450,10 +8360,9 @@
         </is>
       </c>
       <c r="B118" s="39" t="n"/>
-      <c r="C118" s="52" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
+      <c r="C118" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D118" s="38" t="inlineStr">
@@ -5471,10 +8380,9 @@
           <t>Cite 4.18</t>
         </is>
       </c>
-      <c r="G118" s="52" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+      <c r="G118" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H118" s="38" t="inlineStr">
@@ -5492,8 +8400,7 @@
       <c r="B119" s="25" t="n"/>
       <c r="C119" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D119" s="34" t="inlineStr">
@@ -5516,8 +8423,7 @@
       </c>
       <c r="G119" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H119" s="34" t="inlineStr">
@@ -5825,8 +8731,7 @@
       <c r="B130" s="25" t="n"/>
       <c r="C130" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D130" s="34" t="inlineStr">
@@ -5851,8 +8756,7 @@
       </c>
       <c r="G130" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H130" s="34" t="inlineStr">
@@ -5896,8 +8800,7 @@
       <c r="B132" s="25" t="n"/>
       <c r="C132" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D132" s="34" t="inlineStr">
@@ -5920,8 +8823,7 @@
       </c>
       <c r="G132" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H132" s="34" t="inlineStr">
@@ -6242,8 +9144,7 @@
       <c r="B144" s="25" t="n"/>
       <c r="C144" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D144" s="34" t="inlineStr">
@@ -6265,8 +9166,7 @@
       </c>
       <c r="G144" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H144" s="34" t="inlineStr">
@@ -6285,8 +9185,7 @@
       <c r="B145" s="25" t="n"/>
       <c r="C145" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D145" s="34" t="inlineStr">
@@ -6309,8 +9208,7 @@
       </c>
       <c r="G145" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H145" s="34" t="inlineStr">
@@ -6329,8 +9227,7 @@
       <c r="B146" s="25" t="n"/>
       <c r="C146" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D146" s="34" t="inlineStr">
@@ -6355,8 +9252,7 @@
       </c>
       <c r="G146" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H146" s="34" t="inlineStr">
@@ -6375,8 +9271,7 @@
       <c r="B147" s="40" t="n"/>
       <c r="C147" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D147" s="40" t="inlineStr">
@@ -6396,8 +9291,7 @@
       </c>
       <c r="G147" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H147" s="40" t="inlineStr">
@@ -6415,8 +9309,7 @@
       <c r="B148" s="25" t="n"/>
       <c r="C148" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D148" s="34" t="inlineStr">
@@ -6440,8 +9333,7 @@
       </c>
       <c r="G148" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H148" s="34" t="inlineStr">
@@ -6461,8 +9353,7 @@
       <c r="B149" s="17" t="n"/>
       <c r="C149" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D149" s="40" t="inlineStr">
@@ -6482,8 +9373,7 @@
       </c>
       <c r="G149" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H149" s="40" t="inlineStr">
@@ -6501,8 +9391,7 @@
       <c r="B150" s="25" t="n"/>
       <c r="C150" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D150" s="34" t="inlineStr">
@@ -6525,8 +9414,7 @@
       </c>
       <c r="G150" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H150" s="34" t="inlineStr">
@@ -6545,8 +9433,7 @@
       <c r="B151" s="25" t="n"/>
       <c r="C151" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D151" s="34" t="inlineStr">
@@ -6569,8 +9456,7 @@
       </c>
       <c r="G151" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H151" s="34" t="inlineStr">
@@ -6589,8 +9475,7 @@
       <c r="B152" s="17" t="n"/>
       <c r="C152" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D152" s="40" t="inlineStr">
@@ -6610,8 +9495,7 @@
       </c>
       <c r="G152" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H152" s="40" t="inlineStr">
@@ -6703,8 +9587,7 @@
       <c r="B155" s="25" t="n"/>
       <c r="C155" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D155" s="34" t="inlineStr">
@@ -6727,8 +9610,7 @@
       </c>
       <c r="G155" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H155" s="34" t="inlineStr">
@@ -6747,8 +9629,7 @@
       <c r="B156" s="25" t="n"/>
       <c r="C156" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D156" s="34" t="inlineStr">
@@ -6771,8 +9652,7 @@
       </c>
       <c r="G156" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H156" s="34" t="inlineStr">
@@ -6791,8 +9671,7 @@
       <c r="B157" s="17" t="n"/>
       <c r="C157" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D157" s="40" t="inlineStr">
@@ -6812,8 +9691,7 @@
       </c>
       <c r="G157" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H157" s="40" t="inlineStr">
@@ -6869,8 +9747,7 @@
       <c r="B159" s="17" t="n"/>
       <c r="C159" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D159" s="40" t="inlineStr">
@@ -6890,8 +9767,7 @@
       </c>
       <c r="G159" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H159" s="40" t="inlineStr">
@@ -6909,8 +9785,7 @@
       <c r="B160" s="25" t="n"/>
       <c r="C160" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D160" s="34" t="inlineStr">
@@ -6935,8 +9810,7 @@
       </c>
       <c r="G160" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H160" s="34" t="inlineStr">
@@ -6956,8 +9830,7 @@
       <c r="B161" s="17" t="n"/>
       <c r="C161" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D161" s="40" t="inlineStr">
@@ -6977,8 +9850,7 @@
       </c>
       <c r="G161" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H161" s="40" t="inlineStr">
@@ -6996,8 +9868,7 @@
       <c r="B162" s="25" t="n"/>
       <c r="C162" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D162" s="34" t="inlineStr">
@@ -7020,8 +9891,7 @@
       </c>
       <c r="G162" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H162" s="37" t="inlineStr">
@@ -7039,8 +9909,7 @@
       <c r="B163" s="25" t="n"/>
       <c r="C163" s="48" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D163" s="34" t="inlineStr">
@@ -7063,8 +9932,7 @@
       </c>
       <c r="G163" s="48" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H163" s="34" t="inlineStr">
@@ -7083,8 +9951,7 @@
       <c r="B164" s="17" t="n"/>
       <c r="C164" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D164" s="40" t="inlineStr">
@@ -7104,8 +9971,7 @@
       </c>
       <c r="G164" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H164" s="40" t="inlineStr">
@@ -7179,8 +10045,7 @@
       <c r="B167" s="17" t="n"/>
       <c r="C167" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D167" s="40" t="inlineStr">
@@ -7200,8 +10065,7 @@
       </c>
       <c r="G167" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H167" s="40" t="inlineStr">
@@ -7249,8 +10113,7 @@
       <c r="B169" s="17" t="n"/>
       <c r="C169" s="47" t="inlineStr">
         <is>
-          <t>No measurable standard.
-Observational review only.</t>
+          <t>No measurable standard. Observational review only.</t>
         </is>
       </c>
       <c r="D169" s="40" t="inlineStr">
@@ -7270,8 +10133,7 @@
       </c>
       <c r="G169" s="47" t="inlineStr">
         <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
         </is>
       </c>
       <c r="H169" s="40" t="inlineStr">
@@ -7322,8 +10184,8 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="E171" s="53" t="n"/>
-      <c r="F171" s="53" t="n"/>
+      <c r="E171" s="52" t="n"/>
+      <c r="F171" s="52" t="n"/>
       <c r="H171" s="34" t="inlineStr">
         <is>
           <t>*Counter surface height shall be 38" max.
@@ -7359,6 +10221,7 @@
         </is>
       </c>
       <c r="B173" s="49" t="n"/>
+      <c r="C173" s="49" t="n"/>
       <c r="D173" s="49" t="n"/>
       <c r="E173" s="49" t="n"/>
       <c r="F173" s="50" t="n"/>
@@ -7446,9 +10309,9 @@
       </c>
     </row>
     <row r="177" ht="72" customHeight="1">
-      <c r="A177" s="54" t="n"/>
+      <c r="A177" s="53" t="n"/>
       <c r="B177" s="32" t="n"/>
-      <c r="D177" s="55" t="n"/>
+      <c r="D177" s="54" t="n"/>
       <c r="E177" s="34" t="inlineStr">
         <is>
           <t>At least 5% or a minimum of one of each unit of fixed seating, tables, or study carrels shall be accessible.  Clearances between the tables or study carrels shall be accessible</t>
@@ -7472,53 +10335,53 @@
       </c>
     </row>
     <row r="178" ht="42" customHeight="1">
-      <c r="A178" s="54" t="n"/>
+      <c r="A178" s="53" t="n"/>
       <c r="B178" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">fixed seating   </t>
         </is>
       </c>
-      <c r="D178" s="55" t="n"/>
-      <c r="E178" s="53" t="n"/>
-      <c r="F178" s="53" t="n"/>
-      <c r="H178" s="53" t="n"/>
+      <c r="D178" s="54" t="n"/>
+      <c r="E178" s="52" t="n"/>
+      <c r="F178" s="52" t="n"/>
+      <c r="H178" s="52" t="n"/>
     </row>
     <row r="179" ht="38.25" customHeight="1">
-      <c r="A179" s="54" t="n"/>
+      <c r="A179" s="53" t="n"/>
       <c r="B179" s="32" t="n"/>
-      <c r="D179" s="55" t="n"/>
-      <c r="E179" s="53" t="n"/>
-      <c r="F179" s="53" t="n"/>
-      <c r="H179" s="53" t="n"/>
+      <c r="D179" s="54" t="n"/>
+      <c r="E179" s="52" t="n"/>
+      <c r="F179" s="52" t="n"/>
+      <c r="H179" s="52" t="n"/>
     </row>
     <row r="180" ht="38.25" customHeight="1">
-      <c r="A180" s="54" t="n"/>
+      <c r="A180" s="53" t="n"/>
       <c r="B180" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">tables         </t>
         </is>
       </c>
-      <c r="D180" s="55" t="n"/>
-      <c r="E180" s="53" t="n"/>
-      <c r="F180" s="53" t="n"/>
-      <c r="H180" s="53" t="n"/>
+      <c r="D180" s="54" t="n"/>
+      <c r="E180" s="52" t="n"/>
+      <c r="F180" s="52" t="n"/>
+      <c r="H180" s="52" t="n"/>
     </row>
     <row r="181" ht="33" customHeight="1">
-      <c r="A181" s="54" t="n"/>
+      <c r="A181" s="53" t="n"/>
       <c r="B181" s="32" t="n"/>
-      <c r="D181" s="55" t="n"/>
-      <c r="E181" s="53" t="n"/>
-      <c r="F181" s="53" t="n"/>
-      <c r="H181" s="53" t="n"/>
+      <c r="D181" s="54" t="n"/>
+      <c r="E181" s="52" t="n"/>
+      <c r="F181" s="52" t="n"/>
+      <c r="H181" s="52" t="n"/>
     </row>
     <row r="182" ht="36" customHeight="1">
-      <c r="A182" s="56" t="n"/>
+      <c r="A182" s="55" t="n"/>
       <c r="B182" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">study carrels   </t>
         </is>
       </c>
-      <c r="D182" s="57" t="n"/>
+      <c r="D182" s="56" t="n"/>
       <c r="E182" s="51" t="n"/>
       <c r="F182" s="51" t="n"/>
       <c r="H182" s="51" t="n"/>
@@ -7676,77 +10539,75 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="58" t="inlineStr">
+    <row r="190" ht="52" customHeight="1">
+      <c r="A190" s="47" t="inlineStr">
         <is>
           <t>STAIRWAYS AND STEPS</t>
         </is>
       </c>
-      <c r="B190" s="58" t="inlineStr">
-        <is>
-          <t>Added 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
-        </is>
-      </c>
-      <c r="C190" s="58" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
-        </is>
-      </c>
-      <c r="D190" s="58" t="inlineStr">
+      <c r="B190" s="47" t="inlineStr">
+        <is>
+          <t>ADDED 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
+        </is>
+      </c>
+      <c r="C190" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
+        </is>
+      </c>
+      <c r="D190" s="47" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E190" s="58" t="inlineStr">
+      <c r="E190" s="47" t="inlineStr">
         <is>
           <t>Cite 4.9</t>
         </is>
       </c>
-      <c r="F190" s="58" t="inlineStr">
+      <c r="F190" s="47" t="inlineStr">
         <is>
           <t>Cite 4.9</t>
         </is>
       </c>
-      <c r="G190" s="58" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
-        </is>
-      </c>
-      <c r="H190" s="58" t="inlineStr">
+      <c r="G190" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
+        </is>
+      </c>
+      <c r="H190" s="47" t="inlineStr">
         <is>
           <t>Cite 504</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="59" t="inlineStr">
+    <row r="191" ht="39" customHeight="1">
+      <c r="A191" s="57" t="inlineStr">
         <is>
           <t>Riser height uniform, max 7"</t>
         </is>
       </c>
-      <c r="B191" s="59" t="n"/>
-      <c r="C191" s="59" t="n"/>
-      <c r="D191" s="59" t="inlineStr">
+      <c r="B191" s="57" t="n"/>
+      <c r="C191" s="57" t="n"/>
+      <c r="D191" s="57" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E191" s="59" t="inlineStr">
+      <c r="E191" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.9.2</t>
         </is>
       </c>
-      <c r="F191" s="59" t="inlineStr">
+      <c r="F191" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.9.2</t>
         </is>
       </c>
-      <c r="G191" s="59" t="n"/>
-      <c r="H191" s="59" t="inlineStr">
+      <c r="G191" s="57" t="n"/>
+      <c r="H191" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 4"-7" uniform
@@ -7754,1029 +10615,1013 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="59" t="inlineStr">
+    <row r="192" ht="26" customHeight="1">
+      <c r="A192" s="57" t="inlineStr">
         <is>
           <t>Tread depth min 11"</t>
         </is>
       </c>
-      <c r="B192" s="59" t="n"/>
-      <c r="C192" s="59" t="n"/>
-      <c r="D192" s="59" t="inlineStr">
+      <c r="B192" s="57" t="n"/>
+      <c r="C192" s="57" t="n"/>
+      <c r="D192" s="57" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E192" s="59" t="inlineStr">
+      <c r="E192" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.9.2</t>
         </is>
       </c>
-      <c r="F192" s="59" t="inlineStr">
+      <c r="F192" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.9.2</t>
         </is>
       </c>
-      <c r="G192" s="59" t="n"/>
-      <c r="H192" s="59" t="inlineStr">
+      <c r="G192" s="57" t="n"/>
+      <c r="H192" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 504.2</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="59" t="inlineStr">
+    <row r="193" ht="26" customHeight="1">
+      <c r="A193" s="57" t="inlineStr">
         <is>
           <t>Handrail height</t>
         </is>
       </c>
-      <c r="B193" s="59" t="n"/>
-      <c r="C193" s="59" t="n"/>
-      <c r="D193" s="59" t="inlineStr">
+      <c r="B193" s="57" t="n"/>
+      <c r="C193" s="57" t="n"/>
+      <c r="D193" s="57" t="inlineStr">
         <is>
           <t>30"-34"</t>
         </is>
       </c>
-      <c r="E193" s="59" t="inlineStr">
+      <c r="E193" s="57" t="inlineStr">
         <is>
           <t>30"-34"
 Cite 4.9.4</t>
         </is>
       </c>
-      <c r="F193" s="59" t="inlineStr">
+      <c r="F193" s="57" t="inlineStr">
         <is>
           <t>34"-38"
 Cite 4.9.4</t>
         </is>
       </c>
-      <c r="G193" s="59" t="n"/>
-      <c r="H193" s="59" t="inlineStr">
+      <c r="G193" s="57" t="n"/>
+      <c r="H193" s="57" t="inlineStr">
         <is>
           <t>34"-38"
 Cite 505.4</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="59" t="inlineStr">
+    <row r="194" ht="26" customHeight="1">
+      <c r="A194" s="57" t="inlineStr">
         <is>
           <t>Nosings (no abrupt underside; max 1-1/2" projection)</t>
         </is>
       </c>
-      <c r="B194" s="59" t="n"/>
-      <c r="C194" s="59" t="n"/>
-      <c r="D194" s="59" t="inlineStr">
+      <c r="B194" s="57" t="n"/>
+      <c r="C194" s="57" t="n"/>
+      <c r="D194" s="57" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E194" s="59" t="inlineStr">
+      <c r="E194" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.9.3</t>
         </is>
       </c>
-      <c r="F194" s="59" t="inlineStr">
+      <c r="F194" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.9.3</t>
         </is>
       </c>
-      <c r="G194" s="59" t="n"/>
-      <c r="H194" s="59" t="inlineStr">
+      <c r="G194" s="57" t="n"/>
+      <c r="H194" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 504.5</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="58" t="inlineStr">
+    <row r="195" ht="52" customHeight="1">
+      <c r="A195" s="47" t="inlineStr">
         <is>
           <t>PASSENGER LOADING ZONES</t>
         </is>
       </c>
-      <c r="B195" s="58" t="inlineStr">
-        <is>
-          <t>Added 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
-        </is>
-      </c>
-      <c r="C195" s="58" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
-        </is>
-      </c>
-      <c r="D195" s="58" t="inlineStr">
+      <c r="B195" s="47" t="inlineStr">
+        <is>
+          <t>ADDED 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
+        </is>
+      </c>
+      <c r="C195" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
+        </is>
+      </c>
+      <c r="D195" s="47" t="inlineStr">
         <is>
           <t>No specific provision identified in this standard; verify</t>
         </is>
       </c>
-      <c r="E195" s="58" t="inlineStr">
+      <c r="E195" s="47" t="inlineStr">
         <is>
           <t>Cite 4.6.5</t>
         </is>
       </c>
-      <c r="F195" s="58" t="inlineStr">
+      <c r="F195" s="47" t="inlineStr">
         <is>
           <t>Cite 4.6.6</t>
         </is>
       </c>
-      <c r="G195" s="58" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
-        </is>
-      </c>
-      <c r="H195" s="58" t="inlineStr">
+      <c r="G195" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
+        </is>
+      </c>
+      <c r="H195" s="47" t="inlineStr">
         <is>
           <t>Cite 209 &amp; 503</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="59" t="inlineStr">
+    <row r="196" ht="39" customHeight="1">
+      <c r="A196" s="57" t="inlineStr">
         <is>
           <t>Access aisle 60" wide x 20 ft long adjacent and parallel to vehicle pull-up space</t>
         </is>
       </c>
-      <c r="B196" s="59" t="n"/>
-      <c r="C196" s="59" t="n"/>
-      <c r="D196" s="59" t="inlineStr">
+      <c r="B196" s="57" t="n"/>
+      <c r="C196" s="57" t="n"/>
+      <c r="D196" s="57" t="inlineStr">
         <is>
           <t>No specific provision identified in this standard; verify</t>
         </is>
       </c>
-      <c r="E196" s="59" t="inlineStr">
+      <c r="E196" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____</t>
         </is>
       </c>
-      <c r="F196" s="59" t="inlineStr">
+      <c r="F196" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.6.6</t>
         </is>
       </c>
-      <c r="G196" s="59" t="n"/>
-      <c r="H196" s="59" t="inlineStr">
+      <c r="G196" s="57" t="n"/>
+      <c r="H196" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 503.3</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="59" t="inlineStr">
+    <row r="197" ht="26" customHeight="1">
+      <c r="A197" s="57" t="inlineStr">
         <is>
           <t>Vertical clearance min 114" at loading zone and vehicle route</t>
         </is>
       </c>
-      <c r="B197" s="59" t="n"/>
-      <c r="C197" s="59" t="n"/>
-      <c r="D197" s="59" t="inlineStr">
+      <c r="B197" s="57" t="n"/>
+      <c r="C197" s="57" t="n"/>
+      <c r="D197" s="57" t="inlineStr">
         <is>
           <t>No specific provision identified in this standard; verify</t>
         </is>
       </c>
-      <c r="E197" s="59" t="inlineStr">
+      <c r="E197" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____</t>
         </is>
       </c>
-      <c r="F197" s="59" t="inlineStr">
+      <c r="F197" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.6.5</t>
         </is>
       </c>
-      <c r="G197" s="59" t="n"/>
-      <c r="H197" s="59" t="inlineStr">
+      <c r="G197" s="57" t="n"/>
+      <c r="H197" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 503.5</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="58" t="inlineStr">
-        <is>
-          <t>Cafeterias cont. (Service Areas)</t>
-        </is>
-      </c>
-      <c r="B198" s="58" t="inlineStr">
-        <is>
-          <t>Added 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
-        </is>
-      </c>
-      <c r="C198" s="58" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
-        </is>
-      </c>
-      <c r="D198" s="58" t="inlineStr">
+    <row r="198" ht="52" customHeight="1">
+      <c r="A198" s="47" t="inlineStr">
+        <is>
+          <t>CAFETERIAS Cont. (Service Areas)</t>
+        </is>
+      </c>
+      <c r="B198" s="47" t="inlineStr">
+        <is>
+          <t>ADDED 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
+        </is>
+      </c>
+      <c r="C198" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
+        </is>
+      </c>
+      <c r="D198" s="47" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E198" s="58" t="inlineStr">
+      <c r="E198" s="47" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="F198" s="58" t="inlineStr">
+      <c r="F198" s="47" t="inlineStr">
         <is>
           <t>Cite 5.5 &amp; 7.3</t>
         </is>
       </c>
-      <c r="G198" s="58" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
-        </is>
-      </c>
-      <c r="H198" s="58" t="inlineStr">
+      <c r="G198" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
+        </is>
+      </c>
+      <c r="H198" s="47" t="inlineStr">
         <is>
           <t>Cite 904</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="59" t="inlineStr">
+    <row r="199" ht="26" customHeight="1">
+      <c r="A199" s="57" t="inlineStr">
         <is>
           <t>Food service line: aisle min 36" clear; tray slide / counter height</t>
         </is>
       </c>
-      <c r="B199" s="59" t="n"/>
-      <c r="C199" s="59" t="n"/>
-      <c r="D199" s="59" t="inlineStr">
+      <c r="B199" s="57" t="n"/>
+      <c r="C199" s="57" t="n"/>
+      <c r="D199" s="57" t="inlineStr">
         <is>
           <t>Counter max 34"</t>
         </is>
       </c>
-      <c r="E199" s="59" t="inlineStr">
+      <c r="E199" s="57" t="inlineStr">
         <is>
           <t>Counter max 34"</t>
         </is>
       </c>
-      <c r="F199" s="59" t="inlineStr">
+      <c r="F199" s="57" t="inlineStr">
         <is>
           <t>Max 36" (tray slide max 34")
 Cite 5.5</t>
         </is>
       </c>
-      <c r="G199" s="59" t="n"/>
-      <c r="H199" s="59" t="inlineStr">
+      <c r="G199" s="57" t="n"/>
+      <c r="H199" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 904.5</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="59" t="inlineStr">
+    <row r="200" ht="26" customHeight="1">
+      <c r="A200" s="57" t="inlineStr">
         <is>
           <t>Self-service shelves, tableware, condiment areas within reach (max 48" forward)</t>
         </is>
       </c>
-      <c r="B200" s="59" t="n"/>
-      <c r="C200" s="59" t="n"/>
-      <c r="D200" s="59" t="inlineStr">
+      <c r="B200" s="57" t="n"/>
+      <c r="C200" s="57" t="n"/>
+      <c r="D200" s="57" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E200" s="59" t="inlineStr">
+      <c r="E200" s="57" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="F200" s="59" t="inlineStr">
+      <c r="F200" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 5.5</t>
         </is>
       </c>
-      <c r="G200" s="59" t="n"/>
-      <c r="H200" s="59" t="inlineStr">
+      <c r="G200" s="57" t="n"/>
+      <c r="H200" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 904.5.1 &amp; 308</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="59" t="inlineStr">
+    <row r="201" ht="26" customHeight="1">
+      <c r="A201" s="57" t="inlineStr">
         <is>
           <t>Checkout: min 1 accessible aisle, 36" clear width; accessible counter height</t>
         </is>
       </c>
-      <c r="B201" s="59" t="n"/>
-      <c r="C201" s="59" t="n"/>
-      <c r="D201" s="59" t="inlineStr">
+      <c r="B201" s="57" t="n"/>
+      <c r="C201" s="57" t="n"/>
+      <c r="D201" s="57" t="inlineStr">
         <is>
           <t>Counter max 34"</t>
         </is>
       </c>
-      <c r="E201" s="59" t="inlineStr">
+      <c r="E201" s="57" t="inlineStr">
         <is>
           <t>Counter max 34"</t>
         </is>
       </c>
-      <c r="F201" s="59" t="inlineStr">
+      <c r="F201" s="57" t="inlineStr">
         <is>
           <t>Max 36"
 Cite 7.3</t>
         </is>
       </c>
-      <c r="G201" s="59" t="n"/>
-      <c r="H201" s="59" t="inlineStr">
+      <c r="G201" s="57" t="n"/>
+      <c r="H201" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 904.3 &amp; 904.4</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="59" t="inlineStr">
+    <row r="202" ht="26" customHeight="1">
+      <c r="A202" s="57" t="inlineStr">
         <is>
           <t>Tray return slot max 48"; clear floor space 30" x 48"</t>
         </is>
       </c>
-      <c r="B202" s="59" t="n"/>
-      <c r="C202" s="59" t="n"/>
-      <c r="D202" s="59" t="inlineStr">
+      <c r="B202" s="57" t="n"/>
+      <c r="C202" s="57" t="n"/>
+      <c r="D202" s="57" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E202" s="59" t="inlineStr">
+      <c r="E202" s="57" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="F202" s="59" t="inlineStr">
+      <c r="F202" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.2</t>
         </is>
       </c>
-      <c r="G202" s="59" t="n"/>
-      <c r="H202" s="59" t="inlineStr">
+      <c r="G202" s="57" t="n"/>
+      <c r="H202" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 308 &amp; 305</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="59" t="inlineStr">
+    <row r="203" ht="39" customHeight="1">
+      <c r="A203" s="57" t="inlineStr">
         <is>
           <t>Beverage stations and vending: highest operable part max 48"; one-hand operation, max 5 lbs; clear floor space 30" x 48"</t>
         </is>
       </c>
-      <c r="B203" s="59" t="n"/>
-      <c r="C203" s="59" t="n"/>
-      <c r="D203" s="59" t="inlineStr">
+      <c r="B203" s="57" t="n"/>
+      <c r="C203" s="57" t="n"/>
+      <c r="D203" s="57" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E203" s="59" t="inlineStr">
+      <c r="E203" s="57" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="F203" s="59" t="inlineStr">
+      <c r="F203" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.27</t>
         </is>
       </c>
-      <c r="G203" s="59" t="n"/>
-      <c r="H203" s="59" t="inlineStr">
+      <c r="G203" s="57" t="n"/>
+      <c r="H203" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 309 &amp; 305</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="58" t="inlineStr">
-        <is>
-          <t>LIBRARIES cont. (Book Drop)</t>
-        </is>
-      </c>
-      <c r="B204" s="58" t="inlineStr">
-        <is>
-          <t>Added 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
-        </is>
-      </c>
-      <c r="C204" s="58" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
-        </is>
-      </c>
-      <c r="D204" s="58" t="inlineStr">
+    <row r="204" ht="52" customHeight="1">
+      <c r="A204" s="47" t="inlineStr">
+        <is>
+          <t>LIBRARIES Cont. (Book Drop)</t>
+        </is>
+      </c>
+      <c r="B204" s="47" t="inlineStr">
+        <is>
+          <t>ADDED 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
+        </is>
+      </c>
+      <c r="C204" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
+        </is>
+      </c>
+      <c r="D204" s="47" t="inlineStr">
         <is>
           <t>No specific provision identified in this standard; verify</t>
         </is>
       </c>
-      <c r="E204" s="58" t="inlineStr">
+      <c r="E204" s="47" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="F204" s="58" t="inlineStr">
+      <c r="F204" s="47" t="inlineStr">
         <is>
           <t>Cite 4.2, 4.27 &amp; 8</t>
         </is>
       </c>
-      <c r="G204" s="58" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
-        </is>
-      </c>
-      <c r="H204" s="58" t="inlineStr">
+      <c r="G204" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
+        </is>
+      </c>
+      <c r="H204" s="47" t="inlineStr">
         <is>
           <t>Cite 305, 308 &amp; 309</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="59" t="inlineStr">
+    <row r="205" ht="39" customHeight="1">
+      <c r="A205" s="57" t="inlineStr">
         <is>
           <t>Drop slot within reach range (max 48" forward; side reach max 54" pre-2010, max 48" 2010 ADA)</t>
         </is>
       </c>
-      <c r="B205" s="59" t="n"/>
-      <c r="C205" s="59" t="n"/>
-      <c r="D205" s="59" t="inlineStr">
+      <c r="B205" s="57" t="n"/>
+      <c r="C205" s="57" t="n"/>
+      <c r="D205" s="57" t="inlineStr">
         <is>
           <t>No specific provision identified in this standard; verify</t>
         </is>
       </c>
-      <c r="E205" s="59" t="inlineStr">
+      <c r="E205" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.2.5/4.2.6</t>
         </is>
       </c>
-      <c r="F205" s="59" t="inlineStr">
+      <c r="F205" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.2.5/4.2.6</t>
         </is>
       </c>
-      <c r="G205" s="59" t="n"/>
-      <c r="H205" s="59" t="inlineStr">
+      <c r="G205" s="57" t="n"/>
+      <c r="H205" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 308</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="59" t="inlineStr">
+    <row r="206" ht="26" customHeight="1">
+      <c r="A206" s="57" t="inlineStr">
         <is>
           <t>Clear floor space 30" x 48" at book drop; on an accessible route</t>
         </is>
       </c>
-      <c r="B206" s="59" t="n"/>
-      <c r="C206" s="59" t="n"/>
-      <c r="D206" s="59" t="inlineStr">
+      <c r="B206" s="57" t="n"/>
+      <c r="C206" s="57" t="n"/>
+      <c r="D206" s="57" t="inlineStr">
         <is>
           <t>No specific provision identified in this standard; verify</t>
         </is>
       </c>
-      <c r="E206" s="59" t="inlineStr">
+      <c r="E206" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____</t>
         </is>
       </c>
-      <c r="F206" s="59" t="inlineStr">
+      <c r="F206" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.2.4 &amp; 4.3</t>
         </is>
       </c>
-      <c r="G206" s="59" t="n"/>
-      <c r="H206" s="59" t="inlineStr">
+      <c r="G206" s="57" t="n"/>
+      <c r="H206" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 305 &amp; 402</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="59" t="inlineStr">
+    <row r="207" ht="39" customHeight="1">
+      <c r="A207" s="57" t="inlineStr">
         <is>
           <t>Operable with one hand, no tight grasping, pinching, or wrist twisting; max 5 lbs force</t>
         </is>
       </c>
-      <c r="B207" s="59" t="n"/>
-      <c r="C207" s="59" t="n"/>
-      <c r="D207" s="59" t="inlineStr">
+      <c r="B207" s="57" t="n"/>
+      <c r="C207" s="57" t="n"/>
+      <c r="D207" s="57" t="inlineStr">
         <is>
           <t>No specific provision identified in this standard; verify</t>
         </is>
       </c>
-      <c r="E207" s="59" t="inlineStr">
+      <c r="E207" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____</t>
         </is>
       </c>
-      <c r="F207" s="59" t="inlineStr">
+      <c r="F207" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.27.4</t>
         </is>
       </c>
-      <c r="G207" s="59" t="n"/>
-      <c r="H207" s="59" t="inlineStr">
+      <c r="G207" s="57" t="n"/>
+      <c r="H207" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 309.4</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="58" t="inlineStr">
+    <row r="208" ht="52" customHeight="1">
+      <c r="A208" s="47" t="inlineStr">
         <is>
           <t>DRESSING, FITTING &amp; LOCKER ROOMS</t>
         </is>
       </c>
-      <c r="B208" s="58" t="inlineStr">
-        <is>
-          <t>Added 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
-        </is>
-      </c>
-      <c r="C208" s="58" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
-        </is>
-      </c>
-      <c r="D208" s="58" t="inlineStr">
+      <c r="B208" s="47" t="inlineStr">
+        <is>
+          <t>ADDED 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
+        </is>
+      </c>
+      <c r="C208" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
+        </is>
+      </c>
+      <c r="D208" s="47" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E208" s="58" t="inlineStr">
+      <c r="E208" s="47" t="inlineStr">
         <is>
           <t>Cite 4.35</t>
         </is>
       </c>
-      <c r="F208" s="58" t="inlineStr">
+      <c r="F208" s="47" t="inlineStr">
         <is>
           <t>Cite 4.35</t>
         </is>
       </c>
-      <c r="G208" s="58" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
-        </is>
-      </c>
-      <c r="H208" s="58" t="inlineStr">
+      <c r="G208" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
+        </is>
+      </c>
+      <c r="H208" s="47" t="inlineStr">
         <is>
           <t>Cite 222, 803 &amp; 903</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="59" t="inlineStr">
+    <row r="209" ht="39" customHeight="1">
+      <c r="A209" s="57" t="inlineStr">
         <is>
           <t>Accessible lockers: min 5% of each type; operable parts max 48", one-hand operation</t>
         </is>
       </c>
-      <c r="B209" s="59" t="n"/>
-      <c r="C209" s="59" t="n"/>
-      <c r="D209" s="59" t="inlineStr">
+      <c r="B209" s="57" t="n"/>
+      <c r="C209" s="57" t="n"/>
+      <c r="D209" s="57" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E209" s="59" t="inlineStr">
+      <c r="E209" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.25</t>
         </is>
       </c>
-      <c r="F209" s="59" t="inlineStr">
+      <c r="F209" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.25</t>
         </is>
       </c>
-      <c r="G209" s="59" t="n"/>
-      <c r="H209" s="59" t="inlineStr">
+      <c r="G209" s="57" t="n"/>
+      <c r="H209" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 225.2.1 &amp; 811</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="59" t="inlineStr">
+    <row r="210" ht="26" customHeight="1">
+      <c r="A210" s="57" t="inlineStr">
         <is>
           <t>Bench: seat 17"-19" high, 20"-24" deep; clear floor space 30" x 48" alongside</t>
         </is>
       </c>
-      <c r="B210" s="59" t="n"/>
-      <c r="C210" s="59" t="n"/>
-      <c r="D210" s="59" t="inlineStr">
+      <c r="B210" s="57" t="n"/>
+      <c r="C210" s="57" t="n"/>
+      <c r="D210" s="57" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E210" s="59" t="inlineStr">
+      <c r="E210" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.35.4</t>
         </is>
       </c>
-      <c r="F210" s="59" t="inlineStr">
+      <c r="F210" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.35.4</t>
         </is>
       </c>
-      <c r="G210" s="59" t="n"/>
-      <c r="H210" s="59" t="inlineStr">
+      <c r="G210" s="57" t="n"/>
+      <c r="H210" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 903</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="59" t="inlineStr">
+    <row r="211" ht="39" customHeight="1">
+      <c r="A211" s="57" t="inlineStr">
         <is>
           <t>Transfer shower: 36" x 36"; seat 17"-19"; grab bars 33"-36"; curb max 1/2"; hand-held hose min 59" (2010)</t>
         </is>
       </c>
-      <c r="B211" s="59" t="n"/>
-      <c r="C211" s="59" t="n"/>
-      <c r="D211" s="59" t="inlineStr">
+      <c r="B211" s="57" t="n"/>
+      <c r="C211" s="57" t="n"/>
+      <c r="D211" s="57" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E211" s="59" t="inlineStr">
+      <c r="E211" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.21</t>
         </is>
       </c>
-      <c r="F211" s="59" t="inlineStr">
+      <c r="F211" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.21</t>
         </is>
       </c>
-      <c r="G211" s="59" t="n"/>
-      <c r="H211" s="59" t="inlineStr">
+      <c r="G211" s="57" t="n"/>
+      <c r="H211" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 608</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="59" t="inlineStr">
+    <row r="212" ht="39" customHeight="1">
+      <c r="A212" s="57" t="inlineStr">
         <is>
           <t>Male / Female / Non-Gender Specific designation recorded per room (California requirement)</t>
         </is>
       </c>
-      <c r="B212" s="59" t="n"/>
-      <c r="C212" s="59" t="n"/>
-      <c r="D212" s="59" t="inlineStr">
+      <c r="B212" s="57" t="n"/>
+      <c r="C212" s="57" t="n"/>
+      <c r="D212" s="57" t="inlineStr">
         <is>
           <t>Record designation</t>
         </is>
       </c>
-      <c r="E212" s="59" t="inlineStr">
+      <c r="E212" s="57" t="inlineStr">
         <is>
           <t>Record designation</t>
         </is>
       </c>
-      <c r="F212" s="59" t="inlineStr">
+      <c r="F212" s="57" t="inlineStr">
         <is>
           <t>Record designation</t>
         </is>
       </c>
-      <c r="G212" s="59" t="n"/>
-      <c r="H212" s="59" t="inlineStr">
+      <c r="G212" s="57" t="n"/>
+      <c r="H212" s="57" t="inlineStr">
         <is>
           <t>Record designation</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="58" t="inlineStr">
+    <row r="213" ht="52" customHeight="1">
+      <c r="A213" s="47" t="inlineStr">
         <is>
           <t>MEDICAL &amp; FIRST-AID AREAS (incl. Nurse's Office)</t>
         </is>
       </c>
-      <c r="B213" s="58" t="inlineStr">
-        <is>
-          <t>Added 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
-        </is>
-      </c>
-      <c r="C213" s="58" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
-        </is>
-      </c>
-      <c r="D213" s="58" t="inlineStr">
+      <c r="B213" s="47" t="inlineStr">
+        <is>
+          <t>ADDED 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
+        </is>
+      </c>
+      <c r="C213" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
+        </is>
+      </c>
+      <c r="D213" s="47" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E213" s="58" t="inlineStr">
+      <c r="E213" s="47" t="inlineStr">
         <is>
           <t>Cite 4.1</t>
         </is>
       </c>
-      <c r="F213" s="58" t="inlineStr">
+      <c r="F213" s="47" t="inlineStr">
         <is>
           <t>Cite 4.1</t>
         </is>
       </c>
-      <c r="G213" s="58" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
-        </is>
-      </c>
-      <c r="H213" s="58" t="inlineStr">
+      <c r="G213" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
+        </is>
+      </c>
+      <c r="H213" s="47" t="inlineStr">
         <is>
           <t>Cite 201</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="59" t="inlineStr">
+    <row r="214" ht="39" customHeight="1">
+      <c r="A214" s="57" t="inlineStr">
         <is>
           <t>Entry door min 32" clear; on accessible route; turning space min 60"; operable parts max 48"</t>
         </is>
       </c>
-      <c r="B214" s="59" t="n"/>
-      <c r="C214" s="59" t="n"/>
-      <c r="D214" s="59" t="inlineStr">
+      <c r="B214" s="57" t="n"/>
+      <c r="C214" s="57" t="n"/>
+      <c r="D214" s="57" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E214" s="59" t="inlineStr">
+      <c r="E214" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.13, 4.3 &amp; 4.2.3</t>
         </is>
       </c>
-      <c r="F214" s="59" t="inlineStr">
+      <c r="F214" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.13, 4.3 &amp; 4.2.3</t>
         </is>
       </c>
-      <c r="G214" s="59" t="n"/>
-      <c r="H214" s="59" t="inlineStr">
+      <c r="G214" s="57" t="n"/>
+      <c r="H214" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 404, 402, 304 &amp; 308</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="58" t="inlineStr">
+    <row r="215" ht="52" customHeight="1">
+      <c r="A215" s="47" t="inlineStr">
         <is>
           <t>PORTABLE / TEMPORARY CLASSROOMS</t>
         </is>
       </c>
-      <c r="B215" s="58" t="inlineStr">
-        <is>
-          <t>Added 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
-        </is>
-      </c>
-      <c r="C215" s="58" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
-        </is>
-      </c>
-      <c r="D215" s="58" t="inlineStr">
+      <c r="B215" s="47" t="inlineStr">
+        <is>
+          <t>ADDED 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
+        </is>
+      </c>
+      <c r="C215" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
+        </is>
+      </c>
+      <c r="D215" s="47" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E215" s="58" t="inlineStr">
+      <c r="E215" s="47" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="F215" s="58" t="inlineStr">
+      <c r="F215" s="47" t="inlineStr">
         <is>
           <t>Cite 4.1.1(4)</t>
         </is>
       </c>
-      <c r="G215" s="58" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
-        </is>
-      </c>
-      <c r="H215" s="58" t="inlineStr">
+      <c r="G215" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
+        </is>
+      </c>
+      <c r="H215" s="47" t="inlineStr">
         <is>
           <t>Cite 201.3</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="59" t="inlineStr">
+    <row r="216" ht="39" customHeight="1">
+      <c r="A216" s="57" t="inlineStr">
         <is>
           <t>Accessible route, ramp, landing, and door provisions apply to portable units (see Routes, Ramps, Doors rows)</t>
         </is>
       </c>
-      <c r="B216" s="59" t="n"/>
-      <c r="C216" s="59" t="n"/>
-      <c r="D216" s="59" t="inlineStr">
+      <c r="B216" s="57" t="n"/>
+      <c r="C216" s="57" t="n"/>
+      <c r="D216" s="57" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="E216" s="59" t="inlineStr">
+      <c r="E216" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____</t>
         </is>
       </c>
-      <c r="F216" s="59" t="inlineStr">
+      <c r="F216" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.1.1(4)</t>
         </is>
       </c>
-      <c r="G216" s="59" t="n"/>
-      <c r="H216" s="59" t="inlineStr">
+      <c r="G216" s="57" t="n"/>
+      <c r="H216" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 201.3</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="58" t="inlineStr">
+    <row r="217" ht="52" customHeight="1">
+      <c r="A217" s="47" t="inlineStr">
         <is>
           <t>SWIMMING POOLS / AQUATIC AREAS</t>
         </is>
       </c>
-      <c r="B217" s="58" t="inlineStr">
-        <is>
-          <t>Added 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
-        </is>
-      </c>
-      <c r="C217" s="58" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
-        </is>
-      </c>
-      <c r="D217" s="58" t="inlineStr">
+      <c r="B217" s="47" t="inlineStr">
+        <is>
+          <t>ADDED 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
+        </is>
+      </c>
+      <c r="C217" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
+        </is>
+      </c>
+      <c r="D217" s="47" t="inlineStr">
         <is>
           <t>No specific provision identified in this standard; verify</t>
         </is>
       </c>
-      <c r="E217" s="58" t="inlineStr">
+      <c r="E217" s="47" t="inlineStr">
         <is>
           <t>No specific provision identified in this standard; verify</t>
         </is>
       </c>
-      <c r="F217" s="58" t="inlineStr">
+      <c r="F217" s="47" t="inlineStr">
         <is>
           <t>No specific provision identified in this standard; verify</t>
         </is>
       </c>
-      <c r="G217" s="58" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
-        </is>
-      </c>
-      <c r="H217" s="58" t="inlineStr">
+      <c r="G217" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
+        </is>
+      </c>
+      <c r="H217" s="47" t="inlineStr">
         <is>
           <t>Cite 242 &amp; 1009</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="59" t="inlineStr">
+    <row r="218" ht="39" customHeight="1">
+      <c r="A218" s="57" t="inlineStr">
         <is>
           <t>Accessible pool entry: lift or sloped entry (2 accessible means required for pools over 300 linear ft of pool wall)</t>
         </is>
       </c>
-      <c r="B218" s="59" t="n"/>
-      <c r="C218" s="59" t="n"/>
-      <c r="D218" s="59" t="inlineStr">
+      <c r="B218" s="57" t="n"/>
+      <c r="C218" s="57" t="n"/>
+      <c r="D218" s="57" t="inlineStr">
         <is>
           <t>No specific provision identified in this standard; verify</t>
         </is>
       </c>
-      <c r="E218" s="59" t="inlineStr">
+      <c r="E218" s="57" t="inlineStr">
         <is>
           <t>No specific provision identified in this standard; verify</t>
         </is>
       </c>
-      <c r="F218" s="59" t="inlineStr">
+      <c r="F218" s="57" t="inlineStr">
         <is>
           <t>Apply route and entry provisions</t>
         </is>
       </c>
-      <c r="G218" s="59" t="n"/>
-      <c r="H218" s="59" t="inlineStr">
+      <c r="G218" s="57" t="n"/>
+      <c r="H218" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 242.2 &amp; 1009</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="58" t="inlineStr">
+    <row r="219" ht="52" customHeight="1">
+      <c r="A219" s="47" t="inlineStr">
         <is>
           <t>ACCESSIBLE MEANS OF EGRESS / AREAS OF RESCUE ASSISTANCE</t>
         </is>
       </c>
-      <c r="B219" s="58" t="inlineStr">
-        <is>
-          <t>Added 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
-        </is>
-      </c>
-      <c r="C219" s="58" t="inlineStr">
-        <is>
-          <t>No measurable standard.
-Observational review only.</t>
-        </is>
-      </c>
-      <c r="D219" s="58" t="inlineStr">
+      <c r="B219" s="47" t="inlineStr">
+        <is>
+          <t>ADDED 7/2026 to align with revised CRR Building Accessibility guide. Verify cites each cycle.</t>
+        </is>
+      </c>
+      <c r="C219" s="47" t="inlineStr">
+        <is>
+          <t>No measurable standard. Observational review only.</t>
+        </is>
+      </c>
+      <c r="D219" s="47" t="inlineStr">
         <is>
           <t>No specific provision identified in this standard; verify</t>
         </is>
       </c>
-      <c r="E219" s="58" t="inlineStr">
+      <c r="E219" s="47" t="inlineStr">
         <is>
           <t>Verify cite against current instrument</t>
         </is>
       </c>
-      <c r="F219" s="58" t="inlineStr">
+      <c r="F219" s="47" t="inlineStr">
         <is>
           <t>Cite 4.1.3(9) &amp; 4.3.11</t>
         </is>
       </c>
-      <c r="G219" s="58" t="inlineStr">
-        <is>
-          <t>See 1991 ADA column
-(ADAAG technical provisions)</t>
-        </is>
-      </c>
-      <c r="H219" s="58" t="inlineStr">
+      <c r="G219" s="47" t="inlineStr">
+        <is>
+          <t>See 1991 ADA (ADAAG technical provisions)</t>
+        </is>
+      </c>
+      <c r="H219" s="47" t="inlineStr">
         <is>
           <t>Cite 207</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="59" t="inlineStr">
+    <row r="220" ht="39" customHeight="1">
+      <c r="A220" s="57" t="inlineStr">
         <is>
           <t>Accessible means of egress provided; areas of rescue assistance with two-way communication where required</t>
         </is>
       </c>
-      <c r="B220" s="59" t="n"/>
-      <c r="C220" s="59" t="n"/>
-      <c r="D220" s="59" t="inlineStr">
+      <c r="B220" s="57" t="n"/>
+      <c r="C220" s="57" t="n"/>
+      <c r="D220" s="57" t="inlineStr">
         <is>
           <t>No specific provision identified in this standard; verify</t>
         </is>
       </c>
-      <c r="E220" s="59" t="inlineStr">
+      <c r="E220" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____</t>
         </is>
       </c>
-      <c r="F220" s="59" t="inlineStr">
+      <c r="F220" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 4.3.11</t>
         </is>
       </c>
-      <c r="G220" s="59" t="n"/>
-      <c r="H220" s="59" t="inlineStr">
+      <c r="G220" s="57" t="n"/>
+      <c r="H220" s="57" t="inlineStr">
         <is>
           <t>Yes _____       No _____
 Cite 207 (refers to IBC)</t>
@@ -8786,30 +11631,30 @@
   </sheetData>
   <autoFilter ref="A1:F188"/>
   <mergeCells count="24">
-    <mergeCell ref="C176:C182"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="D183:D184"/>
     <mergeCell ref="A187:A188"/>
-    <mergeCell ref="C187:C188"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="F170:F172"/>
     <mergeCell ref="F177:F182"/>
+    <mergeCell ref="D185:D186"/>
     <mergeCell ref="A174:A175"/>
     <mergeCell ref="A183:A184"/>
+    <mergeCell ref="B111:F111"/>
     <mergeCell ref="E177:E182"/>
-    <mergeCell ref="C183:C184"/>
+    <mergeCell ref="H177:H182"/>
     <mergeCell ref="B187:B188"/>
-    <mergeCell ref="A91:F91"/>
     <mergeCell ref="A185:A186"/>
+    <mergeCell ref="D176:D182"/>
     <mergeCell ref="B183:B184"/>
+    <mergeCell ref="A173:F173"/>
+    <mergeCell ref="B174:B175"/>
     <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="D170:D172"/>
-    <mergeCell ref="B111:E111"/>
     <mergeCell ref="A176:A182"/>
     <mergeCell ref="B185:B186"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="D177:D182"/>
+    <mergeCell ref="A91:H91"/>
+    <mergeCell ref="D187:D188"/>
     <mergeCell ref="E170:E172"/>
-    <mergeCell ref="A173:E173"/>
-    <mergeCell ref="C185:C186"/>
   </mergeCells>
   <pageMargins left="0.4143229166666667" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" scale="88" fitToHeight="0"/>
@@ -8868,11 +11713,12 @@
     <brk id="172" min="0" max="16383" man="1"/>
     <brk id="182" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing r:id="rId1000"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -8921,11 +11767,12 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="598"/>
+  <drawing r:id="rId1000"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -9026,6 +11873,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="598"/>
+  <drawing r:id="rId1000"/>
 </worksheet>
 </file>
 
